--- a/Collections/EURO/Netherlands/#EURO#Netherlands#Regular#[1999-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Netherlands/#EURO#Netherlands#Regular#[1999-present]#circulation_quality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Netherlands\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2434308-FE14-4C95-B48D-8F4E93851183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{712F65D2-5F1D-480B-B5E4-2FEE1FA73543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1cent" sheetId="4" r:id="rId1"/>
@@ -46,6 +46,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -388,7 +391,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="153">
   <si>
     <t>Year</t>
   </si>
@@ -766,60 +769,18 @@
     <t>45.769</t>
   </si>
   <si>
-    <t>43.620</t>
-  </si>
-  <si>
     <t>30.028.269</t>
   </si>
   <si>
-    <t>10.034.120</t>
-  </si>
-  <si>
     <t>15.038.269</t>
   </si>
   <si>
-    <t>55.769</t>
-  </si>
-  <si>
-    <t>51.620</t>
-  </si>
-  <si>
     <t>53.769</t>
   </si>
   <si>
-    <t>63.620</t>
-  </si>
-  <si>
-    <t>50.000</t>
-  </si>
-  <si>
-    <t>26.000</t>
-  </si>
-  <si>
     <t>Obv: Mint director Symbol -  Raven</t>
   </si>
   <si>
-    <t>43.621</t>
-  </si>
-  <si>
-    <t>1.050.000</t>
-  </si>
-  <si>
-    <t>2.050.000</t>
-  </si>
-  <si>
-    <t>25.000.000</t>
-  </si>
-  <si>
-    <t>3.050.000</t>
-  </si>
-  <si>
-    <t>20.500</t>
-  </si>
-  <si>
-    <t>33.500</t>
-  </si>
-  <si>
     <t>Subject</t>
   </si>
   <si>
@@ -836,13 +797,67 @@
   </si>
   <si>
     <t>Subtype_2#Map_of_Europe</t>
+  </si>
+  <si>
+    <t>40.023</t>
+  </si>
+  <si>
+    <t>40.022</t>
+  </si>
+  <si>
+    <t>43.521</t>
+  </si>
+  <si>
+    <t>43.520</t>
+  </si>
+  <si>
+    <t>14.000</t>
+  </si>
+  <si>
+    <t>22.500</t>
+  </si>
+  <si>
+    <t>16.500</t>
+  </si>
+  <si>
+    <t>3.040.000</t>
+  </si>
+  <si>
+    <t>25.040.000</t>
+  </si>
+  <si>
+    <t>10.000.000</t>
+  </si>
+  <si>
+    <t>28.500</t>
+  </si>
+  <si>
+    <t>Obv: Without mint symbol - Staff of Mercury</t>
+  </si>
+  <si>
+    <t>Obv: Without mint director Symbol -  St. Servatius Bridge</t>
+  </si>
+  <si>
+    <t>2.040.022</t>
+  </si>
+  <si>
+    <t>12.040.023</t>
+  </si>
+  <si>
+    <t>1.040.022</t>
+  </si>
+  <si>
+    <t>16.040.023</t>
+  </si>
+  <si>
+    <t>5.040.023</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -907,14 +922,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -1066,7 +1073,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1154,22 +1161,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Гиперссылка" xfId="2" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="77">
+  <dxfs count="100">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1763,6 +1768,191 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1794,9 +1984,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="99"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="98" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="97"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2096,13 +2286,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="28"/>
       <c r="B2" s="26" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>32</v>
@@ -2680,7 +2870,7 @@
         <v>42</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>53</v>
@@ -2701,10 +2891,10 @@
         <v>33</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>53</v>
@@ -2725,10 +2915,10 @@
         <v>33</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>53</v>
@@ -2749,10 +2939,10 @@
         <v>33</v>
       </c>
       <c r="D29" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" s="25" t="s">
         <v>135</v>
-      </c>
-      <c r="E29" s="25" t="s">
-        <v>118</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>53</v>
@@ -2762,11 +2952,53 @@
         <v/>
       </c>
     </row>
+    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" s="3" t="str">
+        <f t="shared" ref="G30:G31" si="4">IF(OR(AND(F30&gt;1,F30&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
     <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31"/>
-      <c r="B31"/>
-      <c r="C31"/>
-      <c r="D31"/>
+      <c r="A31" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G31" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32"/>
@@ -2788,12 +3020,12 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F19 F21">
-    <cfRule type="containsText" dxfId="76" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="96" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F19 F21">
-    <cfRule type="colorScale" priority="24">
+    <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2805,11 +3037,28 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22 F24">
-    <cfRule type="containsText" dxfId="75" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="95" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22 F24">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="containsText" dxfId="94" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2821,13 +3070,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="containsText" dxfId="74" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="colorScale" priority="18">
+  <conditionalFormatting sqref="F23">
+    <cfRule type="containsText" dxfId="93" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2838,13 +3087,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="containsText" dxfId="73" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="colorScale" priority="16">
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="92" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2855,12 +3104,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F25">
-    <cfRule type="containsText" dxfId="72" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25">
+  <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="91" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27">
+    <cfRule type="containsText" dxfId="90" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2872,12 +3138,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F26">
-    <cfRule type="containsText" dxfId="71" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F26">
+  <conditionalFormatting sqref="F28">
+    <cfRule type="containsText" dxfId="89" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2889,12 +3155,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F27">
-    <cfRule type="containsText" dxfId="70" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F27">
+  <conditionalFormatting sqref="F29">
+    <cfRule type="containsText" dxfId="88" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2906,12 +3172,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F28">
-    <cfRule type="containsText" dxfId="69" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F28">
+  <conditionalFormatting sqref="F30">
+    <cfRule type="containsText" dxfId="87" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2923,12 +3189,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F29">
-    <cfRule type="containsText" dxfId="68" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F29">
+  <conditionalFormatting sqref="F31">
+    <cfRule type="containsText" dxfId="86" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F31))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2979,13 +3245,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="28"/>
       <c r="B2" s="26" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>32</v>
@@ -3015,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="str">
-        <f t="shared" ref="G3:G29" si="0">IF(OR(AND(F3&gt;1,F3&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G3:G31" si="0">IF(OR(AND(F3&gt;1,F3&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
       <c r="I3" s="5"/>
@@ -3563,7 +3829,7 @@
         <v>42</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>53</v>
@@ -3584,10 +3850,10 @@
         <v>33</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>53</v>
@@ -3608,10 +3874,10 @@
         <v>33</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>53</v>
@@ -3632,10 +3898,10 @@
         <v>33</v>
       </c>
       <c r="D29" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" s="25" t="s">
         <v>135</v>
-      </c>
-      <c r="E29" s="25" t="s">
-        <v>118</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>53</v>
@@ -3645,8 +3911,53 @@
         <v/>
       </c>
     </row>
+    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
     <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="33"/>
+      <c r="A31" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G31" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="B2:E2" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
@@ -3655,12 +3966,12 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F19 F21">
-    <cfRule type="containsText" dxfId="67" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="85" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F19 F21">
-    <cfRule type="colorScale" priority="24">
+    <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3672,11 +3983,62 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22 F24">
-    <cfRule type="containsText" dxfId="66" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="84" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22 F24">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="containsText" dxfId="83" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23">
+    <cfRule type="containsText" dxfId="82" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="81" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3688,12 +4050,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="containsText" dxfId="65" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
+  <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="80" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3705,29 +4067,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="containsText" dxfId="64" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25">
-    <cfRule type="containsText" dxfId="63" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25">
+  <conditionalFormatting sqref="F27">
+    <cfRule type="containsText" dxfId="79" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3739,13 +4084,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F26">
-    <cfRule type="containsText" dxfId="62" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F26">
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="F30">
+    <cfRule type="containsText" dxfId="78" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3756,12 +4101,46 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F27">
-    <cfRule type="containsText" dxfId="61" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F27">
+  <conditionalFormatting sqref="F31">
+    <cfRule type="containsText" dxfId="77" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F31))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28">
+    <cfRule type="containsText" dxfId="76" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29">
+    <cfRule type="containsText" dxfId="75" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3773,40 +4152,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F28">
-    <cfRule type="containsText" dxfId="60" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F28">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F29">
-    <cfRule type="containsText" dxfId="59" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F29">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -3815,7 +4160,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -3846,13 +4191,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="28"/>
       <c r="B2" s="26" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>32</v>
@@ -4406,13 +4751,13 @@
         <v>42</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
       </c>
       <c r="G25" s="3" t="str">
-        <f t="shared" ref="G25:G27" si="1">IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G25:G28" si="1">IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -4424,13 +4769,13 @@
         <v>35</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>33</v>
+        <v>146</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>42</v>
+        <v>147</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -4442,7 +4787,7 @@
     </row>
     <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>35</v>
@@ -4451,22 +4796,19 @@
         <v>33</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>135</v>
+        <v>42</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G27" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="G27" s="3"/>
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>35</v>
@@ -4475,39 +4817,111 @@
         <v>33</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="F28" s="1">
-        <v>0</v>
+        <v>128</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="G28" s="3" t="str">
-        <f t="shared" ref="G28:G29" si="2">IF(OR(AND(F28&gt;1,F28&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="10">
+        <v>2022</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="str">
+        <f t="shared" ref="G29:G32" si="2">IF(OR(AND(F29&gt;1,F29&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="10">
         <v>2023</v>
       </c>
-      <c r="B29" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="E29" s="13" t="s">
+      <c r="B30" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="F29" s="1">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3" t="str">
+      <c r="F31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G31" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G32" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -4519,11 +4933,1253 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F19 F21:F22 F24">
+    <cfRule type="containsText" dxfId="74" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F19 F21:F22 F24">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="containsText" dxfId="73" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23">
+    <cfRule type="containsText" dxfId="72" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="71" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="70" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29">
+    <cfRule type="containsText" dxfId="69" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30">
+    <cfRule type="containsText" dxfId="68" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28">
+    <cfRule type="containsText" dxfId="67" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27">
+    <cfRule type="containsText" dxfId="66" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31">
+    <cfRule type="containsText" dxfId="65" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F31))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F32">
+    <cfRule type="containsText" dxfId="64" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F32">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:J34"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="50.6328125" style="4" customWidth="1"/>
+    <col min="3" max="6" width="33.6328125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="12.6328125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="3.6328125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="12.6328125" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="31"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="28"/>
+      <c r="B2" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10">
+        <v>1999</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="12"/>
+      <c r="G3" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="str">
+        <f t="shared" ref="I3:I30" si="0">IF(OR(AND(H3&gt;1,H3&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="10">
+        <v>2000</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="10">
+        <v>2001</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="12"/>
+      <c r="G5" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="10">
+        <v>2002</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="10">
+        <v>2003</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J7" s="5"/>
+    </row>
+    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="10">
+        <v>2004</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="12"/>
+      <c r="G8" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="10">
+        <v>2005</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="12"/>
+      <c r="G9" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="10">
+        <v>2006</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="10">
+        <v>2007</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="12"/>
+      <c r="G11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="10">
+        <v>2008</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="12"/>
+      <c r="G12" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="10">
+        <v>2009</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="10">
+        <v>2010</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="10">
+        <v>2011</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="12"/>
+      <c r="G15" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="10">
+        <v>2012</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="12"/>
+      <c r="G16" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="10">
+        <v>2012</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17" s="3" t="str">
+        <f t="shared" ref="I17" si="1">IF(OR(AND(H17&gt;1,H17&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="10">
+        <v>2013</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="12"/>
+      <c r="G18" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="10">
+        <v>2014</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="12"/>
+      <c r="G19" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="10">
+        <v>2014</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G20" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="str">
+        <f t="shared" ref="I20" si="2">IF(OR(AND(H20&gt;1,H20&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="10">
+        <v>2015</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="12"/>
+      <c r="G21" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="10">
+        <v>2015</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="12"/>
+      <c r="G22" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I22" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="10">
+        <v>2016</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="12"/>
+      <c r="G23" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="10">
+        <v>2016</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G24" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I24" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2017</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" s="12"/>
+      <c r="G25" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2017</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="12"/>
+      <c r="G26" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I26" s="3"/>
+    </row>
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="10">
+        <v>2018</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="12"/>
+      <c r="G27" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="10">
+        <v>2019</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" s="12"/>
+      <c r="G28" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="10">
+        <v>2020</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" s="12"/>
+      <c r="G29" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I29" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="10">
+        <v>2021</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F30" s="12"/>
+      <c r="G30" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I30" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="10">
+        <v>2022</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F31" s="12"/>
+      <c r="G31" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3" t="str">
+        <f t="shared" ref="I30:I34" si="3">IF(OR(AND(H31&gt;1,H31&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="10">
+        <v>2023</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32" s="12"/>
+      <c r="G32" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F33" s="12"/>
+      <c r="G33" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I33" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F34" s="12"/>
+      <c r="G34" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I34" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:G2" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:F1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H3:H16 H18:H19 H21 H23 H25 H27">
+    <cfRule type="containsText" dxfId="63" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H16 H18:H19 H21 H23 H25 H27">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17">
+    <cfRule type="containsText" dxfId="62" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="61" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22">
+    <cfRule type="containsText" dxfId="60" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H24">
+    <cfRule type="containsText" dxfId="59" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H24">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H26">
     <cfRule type="containsText" dxfId="58" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F19 F21:F22 F24">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H26">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4535,12 +6191,1018 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="containsText" dxfId="57" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
+  <conditionalFormatting sqref="H28">
+    <cfRule type="containsText" dxfId="57" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="containsText" dxfId="56" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H32">
+    <cfRule type="containsText" dxfId="55" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30">
+    <cfRule type="containsText" dxfId="54" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H31">
+    <cfRule type="containsText" dxfId="53" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H31))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H31">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H32">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H33">
+    <cfRule type="containsText" dxfId="50" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H33">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H34">
+    <cfRule type="containsText" dxfId="49" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H34">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="50.6328125" style="4" customWidth="1"/>
+    <col min="3" max="5" width="33.6328125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="12.6328125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="3.6328125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="12.6328125" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="31"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="28"/>
+      <c r="B2" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10">
+        <v>1999</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="str">
+        <f t="shared" ref="H3:H24" si="0">IF(OR(AND(G3&gt;1,G3&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="10">
+        <v>2000</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="10">
+        <v>2001</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="10">
+        <v>2002</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="10">
+        <v>2003</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="10">
+        <v>2004</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="10">
+        <v>2005</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="10">
+        <v>2006</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="10">
+        <v>2007</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="10">
+        <v>2008</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="10">
+        <v>2009</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="10">
+        <v>2010</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="10">
+        <v>2011</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="10">
+        <v>2012</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="10">
+        <v>2013</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="10">
+        <v>2014</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="10">
+        <v>2015</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="10">
+        <v>2015</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="10">
+        <v>2016</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="10">
+        <v>2017</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="10">
+        <v>2017</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H23" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="10">
+        <v>2018</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2019</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H25" s="3" t="str">
+        <f t="shared" ref="H25:H31" si="1">IF(OR(AND(G25&gt;1,G25&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2020</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H26" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="10">
+        <v>2021</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H27" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="10">
+        <v>2022</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="10">
+        <v>2023</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F30" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F31" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H31" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:F2" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:E1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G3:G19 G24 G21">
+    <cfRule type="containsText" dxfId="48" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G19 G24 G21">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22">
+    <cfRule type="containsText" dxfId="47" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
+    <cfRule type="containsText" dxfId="46" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G23">
+    <cfRule type="containsText" dxfId="45" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4552,12 +7214,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="containsText" dxfId="56" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
+  <conditionalFormatting sqref="G23">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4569,12 +7226,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F25">
-    <cfRule type="containsText" dxfId="55" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25">
+  <conditionalFormatting sqref="G25">
+    <cfRule type="containsText" dxfId="44" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G25">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G26">
+    <cfRule type="containsText" dxfId="43" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G26">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4586,12 +7260,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F26">
-    <cfRule type="containsText" dxfId="54" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F26">
+  <conditionalFormatting sqref="G27">
+    <cfRule type="containsText" dxfId="42" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G27">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4603,12 +7277,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F28">
-    <cfRule type="containsText" dxfId="53" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F28">
+  <conditionalFormatting sqref="G28">
+    <cfRule type="containsText" dxfId="41" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G28">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G29">
+    <cfRule type="containsText" dxfId="40" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G29">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4620,12 +7311,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F29">
-    <cfRule type="containsText" dxfId="52" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F29">
+  <conditionalFormatting sqref="G30">
+    <cfRule type="containsText" dxfId="39" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G30">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4637,12 +7328,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F27">
-    <cfRule type="containsText" dxfId="51" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F27">
+  <conditionalFormatting sqref="G31">
+    <cfRule type="containsText" dxfId="38" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G31))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G31">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4660,8 +7351,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
@@ -4687,27 +7378,27 @@
       <c r="G1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="23" t="s">
-        <v>6</v>
+      <c r="H1" s="22" t="s">
+        <v>10</v>
       </c>
       <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="28"/>
       <c r="B2" s="26" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>32</v>
@@ -4735,15 +7426,16 @@
       </c>
       <c r="F3" s="12"/>
       <c r="G3" s="13" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="H3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="3" t="str">
-        <f t="shared" ref="I3:I29" si="0">IF(OR(AND(H3&gt;1,H3&lt;&gt;"-")),"Can exchange","")</f>
-        <v/>
-      </c>
+        <f t="shared" ref="I3:I32" si="0">IF(OR(AND(H3&gt;1,H3&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+      <c r="J3" s="5"/>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
@@ -4763,7 +7455,7 @@
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="13" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
@@ -4772,6 +7464,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
+      <c r="J4" s="5"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
@@ -4791,7 +7484,7 @@
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="13" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -4819,7 +7512,7 @@
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="13" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -4828,7 +7521,6 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J6" s="5"/>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
@@ -4857,7 +7549,6 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J7" s="5"/>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
@@ -4877,7 +7568,7 @@
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="13" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -5101,7 +7792,7 @@
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="13" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>
@@ -5113,7 +7804,7 @@
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>34</v>
@@ -5127,26 +7818,24 @@
       <c r="E17" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="G17" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>53</v>
+      <c r="F17" s="12"/>
+      <c r="G17" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
       </c>
       <c r="I17" s="3" t="str">
-        <f t="shared" ref="I17" si="1">IF(OR(AND(H17&gt;1,H17&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>33</v>
@@ -5159,7 +7848,7 @@
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="13" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -5171,7 +7860,7 @@
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>35</v>
@@ -5187,7 +7876,7 @@
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="13" t="s">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="H19" s="1">
         <v>0</v>
@@ -5199,7 +7888,7 @@
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="10">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>35</v>
@@ -5211,25 +7900,23 @@
         <v>8</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>116</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F20" s="12"/>
       <c r="G20" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
+        <v>109</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="I20" s="3" t="str">
-        <f t="shared" ref="I20" si="2">IF(OR(AND(H20&gt;1,H20&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>35</v>
@@ -5241,7 +7928,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="13" t="s">
@@ -5257,7 +7944,7 @@
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>35</v>
@@ -5273,7 +7960,7 @@
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="25" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>53</v>
@@ -5285,7 +7972,7 @@
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>35</v>
@@ -5299,21 +7986,23 @@
       <c r="E23" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="12"/>
-      <c r="G23" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="H23" s="1">
-        <v>0</v>
+      <c r="F23" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="G23" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="I23" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I23" si="1">IF(OR(AND(H23&gt;1,H23&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="10">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>35</v>
@@ -5325,13 +8014,11 @@
         <v>8</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>116</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F24" s="12"/>
       <c r="G24" s="25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>53</v>
@@ -5343,7 +8030,7 @@
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>35</v>
@@ -5355,14 +8042,14 @@
         <v>8</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F25" s="12"/>
-      <c r="G25" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
+      <c r="G25" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="I25" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5371,7 +8058,7 @@
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>35</v>
@@ -5387,16 +8074,19 @@
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="25" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I26" s="3"/>
+      <c r="I26" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>35</v>
@@ -5411,11 +8101,11 @@
         <v>42</v>
       </c>
       <c r="F27" s="12"/>
-      <c r="G27" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="H27" s="1">
-        <v>0</v>
+      <c r="G27" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="I27" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5424,7 +8114,7 @@
     </row>
     <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>35</v>
@@ -5436,14 +8126,14 @@
         <v>8</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="F28" s="12"/>
-      <c r="G28" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="H28" s="1">
-        <v>0</v>
+      <c r="G28" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="I28" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5452,7 +8142,7 @@
     </row>
     <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="10">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>35</v>
@@ -5464,11 +8154,11 @@
         <v>8</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="F29" s="12"/>
       <c r="G29" s="25" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>53</v>
@@ -5480,7 +8170,7 @@
     </row>
     <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>35</v>
@@ -5492,23 +8182,23 @@
         <v>8</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="F30" s="12"/>
-      <c r="G30" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>53</v>
+      <c r="G30" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
       </c>
       <c r="I30" s="3" t="str">
-        <f t="shared" ref="I30:I32" si="3">IF(OR(AND(H30&gt;1,H30&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>35</v>
@@ -5520,23 +8210,23 @@
         <v>8</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="F31" s="12"/>
-      <c r="G31" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="H31" s="1">
-        <v>0</v>
+      <c r="G31" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="I31" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>35</v>
@@ -5548,32 +8238,66 @@
         <v>8</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="F32" s="12"/>
-      <c r="G32" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="H32" s="1">
-        <v>0</v>
+      <c r="G32" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="I32" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:G2" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
+  <autoFilter ref="B2:G2" xr:uid="{00000000-0001-0000-0500-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H3:H16 H18:H19 H21 H23 H25 H27">
-    <cfRule type="containsText" dxfId="50" priority="31" operator="containsText" text="*-">
+  <conditionalFormatting sqref="H3:H19 H21 H25">
+    <cfRule type="containsText" dxfId="37" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H16 H18:H19 H21 H23 H25 H27">
+  <conditionalFormatting sqref="H3:H19 H21 H25">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22">
+    <cfRule type="containsText" dxfId="36" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="35" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5585,12 +8309,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17">
-    <cfRule type="containsText" dxfId="49" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H17">
+  <conditionalFormatting sqref="H24">
+    <cfRule type="containsText" dxfId="34" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H24">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H23">
+    <cfRule type="containsText" dxfId="33" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H23">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5602,80 +8343,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H20">
-    <cfRule type="containsText" dxfId="48" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H20">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22">
-    <cfRule type="containsText" dxfId="47" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H24">
-    <cfRule type="containsText" dxfId="46" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H24">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H26">
-    <cfRule type="containsText" dxfId="45" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H26">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
-    <cfRule type="containsText" dxfId="44" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
+  <conditionalFormatting sqref="H27">
+    <cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5687,12 +8360,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
-    <cfRule type="containsText" dxfId="43" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
+  <conditionalFormatting sqref="H28">
+    <cfRule type="containsText" dxfId="31" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5704,13 +8377,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H32">
-    <cfRule type="containsText" dxfId="42" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H30">
-    <cfRule type="containsText" dxfId="41" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5726,8 +8394,42 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="containsText" dxfId="28" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H26">
+    <cfRule type="containsText" dxfId="27" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H26">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="containsText" dxfId="40" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H31))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5744,6 +8446,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32">
+    <cfRule type="containsText" dxfId="22" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H32">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5761,9 +8468,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H29"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -5774,7 +8481,7 @@
     <col min="8" max="8" width="12.6328125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -5787,24 +8494,24 @@
       <c r="F1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="23" t="s">
-        <v>9</v>
+      <c r="G1" s="22" t="s">
+        <v>11</v>
       </c>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="28"/>
       <c r="B2" s="26" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>32</v>
@@ -5814,7 +8521,7 @@
       </c>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
         <v>1999</v>
       </c>
@@ -5831,17 +8538,17 @@
         <v>37</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
       </c>
       <c r="H3" s="3" t="str">
-        <f t="shared" ref="H3:H24" si="0">IF(OR(AND(G3&gt;1,G3&lt;&gt;"-")),"Can exchange","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" ref="H3:H25" si="0">IF(OR(AND(G3&gt;1,G3&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <v>2000</v>
       </c>
@@ -5858,17 +8565,18 @@
         <v>36</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I4" s="14"/>
+    </row>
+    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>2001</v>
       </c>
@@ -5885,7 +8593,7 @@
         <v>38</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -5895,7 +8603,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
         <v>2002</v>
       </c>
@@ -5912,17 +8620,17 @@
         <v>39</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <v>2003</v>
       </c>
@@ -5939,7 +8647,7 @@
         <v>40</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -5949,7 +8657,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
         <v>2004</v>
       </c>
@@ -5966,7 +8674,7 @@
         <v>40</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -5976,7 +8684,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
         <v>2005</v>
       </c>
@@ -5993,7 +8701,7 @@
         <v>40</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -6003,7 +8711,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10">
         <v>2006</v>
       </c>
@@ -6030,7 +8738,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <v>2007</v>
       </c>
@@ -6047,7 +8755,7 @@
         <v>40</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -6057,7 +8765,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10">
         <v>2008</v>
       </c>
@@ -6084,7 +8792,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10">
         <v>2009</v>
       </c>
@@ -6101,7 +8809,7 @@
         <v>40</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -6111,7 +8819,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10">
         <v>2010</v>
       </c>
@@ -6138,7 +8846,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10">
         <v>2011</v>
       </c>
@@ -6165,7 +8873,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10">
         <v>2012</v>
       </c>
@@ -6209,7 +8917,7 @@
         <v>40</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -6263,7 +8971,7 @@
         <v>40</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -6317,7 +9025,7 @@
         <v>41</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
@@ -6344,7 +9052,7 @@
         <v>41</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>53</v>
@@ -6397,11 +9105,11 @@
       <c r="E24" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F24" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
+      <c r="F24" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="H24" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6425,13 +9133,13 @@
         <v>42</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>53</v>
       </c>
       <c r="H25" s="3" t="str">
-        <f t="shared" ref="H25:H29" si="1">IF(OR(AND(G25&gt;1,G25&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -6452,13 +9160,13 @@
         <v>42</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>53</v>
       </c>
       <c r="H26" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H26:H31" si="1">IF(OR(AND(G26&gt;1,G26&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -6476,10 +9184,10 @@
         <v>8</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>53</v>
@@ -6503,13 +9211,13 @@
         <v>8</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0</v>
+        <v>128</v>
+      </c>
+      <c r="F28" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="H28" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6530,32 +9238,87 @@
         <v>8</v>
       </c>
       <c r="E29" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F29" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="G29" s="1">
-        <v>0</v>
+      <c r="G29" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="H29" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
+    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F30" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F31" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H31" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:F2" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
+  <autoFilter ref="B2:F2" xr:uid="{00000000-0001-0000-0600-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G3:G19 G24 G21">
-    <cfRule type="containsText" dxfId="39" priority="25" operator="containsText" text="*-">
+  <phoneticPr fontId="9" type="noConversion"/>
+  <conditionalFormatting sqref="G3:G19 G21">
+    <cfRule type="containsText" dxfId="21" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G19 G24 G21">
-    <cfRule type="colorScale" priority="26">
+  <conditionalFormatting sqref="G3:G19 G21">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -6566,34 +9329,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G22">
-    <cfRule type="containsText" dxfId="38" priority="21" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G22 G24">
+    <cfRule type="containsText" dxfId="20" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G22))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G22">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G20">
-    <cfRule type="containsText" dxfId="37" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G23">
-    <cfRule type="containsText" dxfId="36" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G20">
+  <conditionalFormatting sqref="G24 G22">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6605,7 +9346,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23">
+  <conditionalFormatting sqref="G20">
+    <cfRule type="containsText" dxfId="19" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6617,13 +9363,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G25">
-    <cfRule type="containsText" dxfId="35" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G25">
-    <cfRule type="colorScale" priority="10">
+  <conditionalFormatting sqref="G23">
+    <cfRule type="containsText" dxfId="18" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G23">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -6634,29 +9380,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G26">
-    <cfRule type="containsText" dxfId="34" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G26))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G26">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G27">
-    <cfRule type="containsText" dxfId="33" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G27">
+  <conditionalFormatting sqref="G25:G29">
+    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G25:G29">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6668,12 +9397,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G28">
-    <cfRule type="containsText" dxfId="32" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G28">
+  <conditionalFormatting sqref="G30">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G30">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6685,12 +9414,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G29">
-    <cfRule type="containsText" dxfId="31" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G29">
+  <conditionalFormatting sqref="G31">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G31))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G31">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6708,9 +9437,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J30"/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -6736,26 +9465,26 @@
         <v>2</v>
       </c>
       <c r="H1" s="22" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="28"/>
       <c r="B2" s="26" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>32</v>
@@ -6783,13 +9512,13 @@
       </c>
       <c r="F3" s="12"/>
       <c r="G3" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="3" t="str">
-        <f t="shared" ref="I3:I30" si="0">IF(OR(AND(H3&gt;1,H3&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="I3:I27" si="0">IF(OR(AND(H3&gt;1,H3&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
       <c r="J3" s="5"/>
@@ -6812,10 +9541,10 @@
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="13" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6841,14 +9570,14 @@
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="13" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" s="3" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Can exchange</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6869,7 +9598,7 @@
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="13" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -6953,7 +9682,7 @@
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="13" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -7009,7 +9738,7 @@
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="13" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -7065,7 +9794,7 @@
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="13" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="H13" s="1">
         <v>0</v>
@@ -7177,7 +9906,7 @@
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="13" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
@@ -7205,7 +9934,7 @@
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="13" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -7233,7 +9962,7 @@
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="13" t="s">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="H19" s="1">
         <v>0</v>
@@ -7289,7 +10018,7 @@
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="13" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
@@ -7317,7 +10046,7 @@
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>53</v>
@@ -7341,19 +10070,17 @@
         <v>8</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>117</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F23" s="12"/>
       <c r="G23" s="25" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>53</v>
       </c>
       <c r="I23" s="3" t="str">
-        <f t="shared" ref="I23" si="1">IF(OR(AND(H23&gt;1,H23&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7373,17 +10100,16 @@
       <c r="E24" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F24" s="12"/>
+      <c r="F24" s="12" t="s">
+        <v>119</v>
+      </c>
       <c r="G24" s="25" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I24" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="I24" s="3"/>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10">
@@ -7403,19 +10129,19 @@
       </c>
       <c r="F25" s="12"/>
       <c r="G25" s="25" t="s">
-        <v>52</v>
+        <v>122</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>53</v>
       </c>
       <c r="I25" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I25" si="1">IF(OR(AND(H25&gt;1,H25&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>35</v>
@@ -7429,21 +10155,23 @@
       <c r="E26" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F26" s="12"/>
+      <c r="F26" s="12" t="s">
+        <v>120</v>
+      </c>
       <c r="G26" s="25" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>53</v>
       </c>
       <c r="I26" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I26" si="2">IF(OR(AND(H26&gt;1,H26&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>35</v>
@@ -7459,7 +10187,7 @@
       </c>
       <c r="F27" s="12"/>
       <c r="G27" s="25" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>53</v>
@@ -7471,7 +10199,7 @@
     </row>
     <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>35</v>
@@ -7483,23 +10211,25 @@
         <v>8</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="F28" s="12"/>
+        <v>42</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>123</v>
+      </c>
       <c r="G28" s="25" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>53</v>
       </c>
       <c r="I28" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I28:I29" si="3">IF(OR(AND(H28&gt;1,H28&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="10">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>35</v>
@@ -7511,23 +10241,23 @@
         <v>8</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>135</v>
+        <v>42</v>
       </c>
       <c r="F29" s="12"/>
       <c r="G29" s="25" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>53</v>
       </c>
       <c r="I29" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>35</v>
@@ -7539,32 +10269,192 @@
         <v>8</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="F30" s="12"/>
       <c r="G30" s="25" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>53</v>
       </c>
       <c r="I30" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I30" si="4">IF(OR(AND(H30&gt;1,H30&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="10">
+        <v>2022</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F31" s="12"/>
+      <c r="G31" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I31" s="3" t="str">
+        <f t="shared" ref="I31" si="5">IF(OR(AND(H31&gt;1,H31&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="10">
+        <v>2023</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32" s="12"/>
+      <c r="G32" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I32" s="3" t="str">
+        <f t="shared" ref="I32:I33" si="6">IF(OR(AND(H32&gt;1,H32&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F33" s="12"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F34" s="12"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3" t="str">
+        <f t="shared" ref="I34" si="7">IF(OR(AND(H34&gt;1,H34&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:G2" xr:uid="{00000000-0001-0000-0500-000000000000}"/>
+  <autoFilter ref="B2:G2" xr:uid="{00000000-0001-0000-0700-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H3:H19 H21 H25">
-    <cfRule type="containsText" dxfId="30" priority="23" operator="containsText" text="*-">
+  <phoneticPr fontId="8" type="noConversion"/>
+  <conditionalFormatting sqref="H3:H19 H21">
+    <cfRule type="containsText" dxfId="15" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H19 H21 H25">
+  <conditionalFormatting sqref="H3:H19 H21">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22">
+    <cfRule type="containsText" dxfId="14" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="13" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H23">
+    <cfRule type="containsText" dxfId="12" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H23">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7576,12 +10466,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22">
-    <cfRule type="containsText" dxfId="29" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22">
+  <conditionalFormatting sqref="H25">
+    <cfRule type="containsText" dxfId="11" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H25">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7593,25 +10483,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H20">
-    <cfRule type="containsText" dxfId="28" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H20">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H24">
-    <cfRule type="containsText" dxfId="27" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="10" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7627,12 +10500,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H23">
-    <cfRule type="containsText" dxfId="26" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H23))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H23">
+  <conditionalFormatting sqref="H26">
+    <cfRule type="containsText" dxfId="9" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H26">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7644,12 +10517,46 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H26">
-    <cfRule type="containsText" dxfId="25" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H26">
+  <conditionalFormatting sqref="H28">
+    <cfRule type="containsText" dxfId="8" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
+    <cfRule type="containsText" dxfId="7" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29:H30">
+    <cfRule type="containsText" dxfId="6" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29:H30">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7661,12 +10568,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H27">
-    <cfRule type="containsText" dxfId="24" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H27">
+  <conditionalFormatting sqref="H31">
+    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H31))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H31">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7678,17 +10585,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H30">
-    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
-    <cfRule type="containsText" dxfId="22" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
+  <conditionalFormatting sqref="H32">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H32">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7700,12 +10602,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
-    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
+  <conditionalFormatting sqref="H33">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H33">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7717,2051 +10619,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H30">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="50.6328125" style="4" customWidth="1"/>
-    <col min="3" max="5" width="33.6328125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.6328125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="3.6328125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" style="4" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="31"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="28"/>
-      <c r="B2" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="10">
-        <v>1999</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="str">
-        <f t="shared" ref="H3:H26" si="0">IF(OR(AND(G3&gt;1,G3&lt;&gt;"-")),"Can exchange","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="10">
-        <v>2000</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I4" s="14"/>
-    </row>
-    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="10">
-        <v>2001</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="10">
-        <v>2002</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="10">
-        <v>2003</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="10">
-        <v>2004</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="10">
-        <v>2005</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="10">
-        <v>2006</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="10">
-        <v>2007</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="10">
-        <v>2008</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="10">
-        <v>2009</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="10">
-        <v>2010</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="10">
-        <v>2011</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="10">
-        <v>2012</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="10">
-        <v>2013</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="10">
-        <v>2014</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="10">
-        <v>2015</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0</v>
-      </c>
-      <c r="H19" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="10">
-        <v>2015</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H20" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="10">
-        <v>2016</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="10">
-        <v>2017</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H22" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="10">
-        <v>2017</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F23" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H23" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="10">
-        <v>2018</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H24" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="10">
-        <v>2019</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F25" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H25" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="10">
-        <v>2019</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H26" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="10">
-        <v>2020</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F27" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H27" s="3" t="str">
-        <f t="shared" ref="H27:H30" si="1">IF(OR(AND(G27&gt;1,G27&lt;&gt;"-")),"Can exchange","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="10">
-        <v>2021</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="F28" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H28" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="10">
-        <v>2022</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="F29" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H29" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="10">
-        <v>2023</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="F30" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H30" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="B2:F2" xr:uid="{00000000-0001-0000-0600-000000000000}"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:E1"/>
-  </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="G3:G19 G21">
-    <cfRule type="containsText" dxfId="20" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G19 G21">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G22 G24">
-    <cfRule type="containsText" dxfId="19" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G22 G24">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G20">
-    <cfRule type="containsText" dxfId="18" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G20">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G23">
-    <cfRule type="containsText" dxfId="17" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G23">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G25">
-    <cfRule type="containsText" dxfId="16" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G25">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G26:G30">
-    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G26))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G26:G30">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="50.6328125" style="4" customWidth="1"/>
-    <col min="3" max="6" width="33.6328125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="12.6328125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="3.6328125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="12.6328125" style="4" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="31"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="2"/>
-    </row>
-    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="28"/>
-      <c r="B2" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="10">
-        <v>1999</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="1">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3" t="str">
-        <f t="shared" ref="I3:I27" si="0">IF(OR(AND(H3&gt;1,H3&lt;&gt;"-")),"Can exchange","")</f>
-        <v/>
-      </c>
-      <c r="J3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="10">
-        <v>2000</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J4" s="5"/>
-    </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="10">
-        <v>2001</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H5" s="1">
-        <v>2</v>
-      </c>
-      <c r="I5" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Can exchange</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="10">
-        <v>2002</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="10">
-        <v>2003</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="10">
-        <v>2004</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="10">
-        <v>2005</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="10">
-        <v>2006</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="10">
-        <v>2007</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="12"/>
-      <c r="G11" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="10">
-        <v>2008</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="12"/>
-      <c r="G12" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="10">
-        <v>2009</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="10">
-        <v>2010</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="10">
-        <v>2011</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="12"/>
-      <c r="G15" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="10">
-        <v>2012</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="12"/>
-      <c r="G16" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="10">
-        <v>2013</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0</v>
-      </c>
-      <c r="I17" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="10">
-        <v>2014</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="12"/>
-      <c r="G18" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="H18" s="1">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="10">
-        <v>2015</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F19" s="12"/>
-      <c r="G19" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="10">
-        <v>2015</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F20" s="12"/>
-      <c r="G20" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I20" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="10">
-        <v>2016</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F21" s="12"/>
-      <c r="G21" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="10">
-        <v>2017</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" s="12"/>
-      <c r="G22" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I22" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="10">
-        <v>2017</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F23" s="12"/>
-      <c r="G23" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I23" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="10">
-        <v>2017</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="G24" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I24" s="3"/>
-    </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="10">
-        <v>2018</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F25" s="12"/>
-      <c r="G25" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I25" s="3" t="str">
-        <f t="shared" ref="I25" si="1">IF(OR(AND(H25&gt;1,H25&lt;&gt;"-")),"Can exchange","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="10">
-        <v>2018</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="G26" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I26" s="3" t="str">
-        <f t="shared" ref="I26" si="2">IF(OR(AND(H26&gt;1,H26&lt;&gt;"-")),"Can exchange","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="10">
-        <v>2019</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F27" s="12"/>
-      <c r="G27" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I27" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="10">
-        <v>2019</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="G28" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I28" s="3" t="str">
-        <f t="shared" ref="I28:I29" si="3">IF(OR(AND(H28&gt;1,H28&lt;&gt;"-")),"Can exchange","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="10">
-        <v>2020</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F29" s="12"/>
-      <c r="G29" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I29" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="10">
-        <v>2021</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="F30" s="12"/>
-      <c r="G30" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I30" s="3" t="str">
-        <f t="shared" ref="I30" si="4">IF(OR(AND(H30&gt;1,H30&lt;&gt;"-")),"Can exchange","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="10">
-        <v>2022</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="F31" s="12"/>
-      <c r="G31" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I31" s="3" t="str">
-        <f t="shared" ref="I31" si="5">IF(OR(AND(H31&gt;1,H31&lt;&gt;"-")),"Can exchange","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="10">
-        <v>2023</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="F32" s="12"/>
-      <c r="G32" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I32" s="3" t="str">
-        <f t="shared" ref="I32" si="6">IF(OR(AND(H32&gt;1,H32&lt;&gt;"-")),"Can exchange","")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="B2:G2" xr:uid="{00000000-0001-0000-0700-000000000000}"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:F1"/>
-  </mergeCells>
-  <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="H3:H19 H21">
-    <cfRule type="containsText" dxfId="14" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H19 H21">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22">
-    <cfRule type="containsText" dxfId="13" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H20">
-    <cfRule type="containsText" dxfId="12" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H20">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H23">
-    <cfRule type="containsText" dxfId="11" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H23))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H23">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H25">
-    <cfRule type="containsText" dxfId="10" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H25">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H24">
-    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H24">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H26">
-    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H26">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
-    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H27">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H27">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H29:H30">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H29:H30">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H31">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H31))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H31">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H32">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H32">
+  <conditionalFormatting sqref="H34">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H34">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
